--- a/docs/เทียบค่าสี-R4.0เว็บ-vs-R3.9 (ฉบับแก้).xlsx
+++ b/docs/เทียบค่าสี-R4.0เว็บ-vs-R3.9 (ฉบับแก้).xlsx
@@ -4242,40 +4242,37 @@
           <t xml:space="preserve">ลายไม้มะฮอกกานี</t>
         </is>
       </c>
-      <c r="H84" s="2">
-        <v>190</v>
+      <c r="H84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ซื้อเส้นสำเร็จ</t>
+        </is>
       </c>
       <c r="I84" s="2">
-        <v>34885</v>
+        <v>25027</v>
       </c>
       <c r="J84" s="2">
-        <v>17387</v>
+        <v>7529</v>
       </c>
       <c r="K84" s="2">
-        <v>41500</v>
+        <v>18000</v>
       </c>
       <c r="L84" s="2">
         <v>4000</v>
       </c>
       <c r="M84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">+937.5%</t>
+          <t xml:space="preserve">+350%</t>
         </is>
       </c>
       <c r="N84" s="2">
-        <v>90600</v>
+        <v>67100</v>
       </c>
       <c r="O84" s="2">
         <v>42800</v>
       </c>
       <c r="P84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">+111.7%</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">เว็บรุ่นนี้ไม่มีสีสต็อกนี้ → คิดเป็นลายไม้อบพิเศษ · รวมค่าเปิดตู้อบ 2000</t>
+          <t xml:space="preserve">+56.8%</t>
         </is>
       </c>
     </row>
@@ -4290,40 +4287,37 @@
           <t xml:space="preserve">ลายไม้ไวท์โอ๊ค</t>
         </is>
       </c>
-      <c r="H85" s="2">
-        <v>190</v>
+      <c r="H85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ซื้อเส้นสำเร็จ</t>
+        </is>
       </c>
       <c r="I85" s="2">
-        <v>34885</v>
+        <v>24787</v>
       </c>
       <c r="J85" s="2">
-        <v>17387</v>
+        <v>7289</v>
       </c>
       <c r="K85" s="2">
-        <v>41500</v>
+        <v>17400</v>
       </c>
       <c r="L85" s="2">
         <v>4000</v>
       </c>
       <c r="M85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">+937.5%</t>
+          <t xml:space="preserve">+335%</t>
         </is>
       </c>
       <c r="N85" s="2">
-        <v>90600</v>
+        <v>66500</v>
       </c>
       <c r="O85" s="2">
         <v>42800</v>
       </c>
       <c r="P85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">+111.7%</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">เว็บรุ่นนี้ไม่มีสีสต็อกนี้ → คิดเป็นลายไม้อบพิเศษ · รวมค่าเปิดตู้อบ 2000</t>
+          <t xml:space="preserve">+55.4%</t>
         </is>
       </c>
     </row>
